--- a/output/pdf_financials_xlsx/DCBO.xlsx
+++ b/output/pdf_financials_xlsx/DCBO.xlsx
@@ -3319,25 +3319,25 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.927</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.335</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-4.243</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>0.555</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>-2.892</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="104">
@@ -3403,25 +3403,25 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>6.87</v>
+        <v>5.943</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>4.086</v>
+        <v>3.751</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>12.123</v>
+        <v>7.88</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>8.254</v>
+        <v>8.478999999999999</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>12.735</v>
+        <v>13.29</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>7.19</v>
+        <v>4.298</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>2.868</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="107">
@@ -4478,7 +4478,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n">
         <v>1.502</v>
       </c>
@@ -8115,7 +8119,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E80" s="5" t="n">
         <v>-0.927</v>
       </c>

--- a/output/pdf_financials_xlsx/DCBO.xlsx
+++ b/output/pdf_financials_xlsx/DCBO.xlsx
@@ -1520,25 +1520,25 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.395</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.475</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.269</v>
       </c>
     </row>
     <row r="41">
@@ -1548,25 +1548,25 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>6.138</v>
+        <v>6.149</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>10.108</v>
+        <v>10.256</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>27.685</v>
+        <v>27.721</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>37.527</v>
+        <v>37.922</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>41.775</v>
+        <v>41.819</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>45.566</v>
+        <v>46.041</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>55.209</v>
+        <v>55.478</v>
       </c>
     </row>
     <row r="42">
@@ -1744,22 +1744,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.745</v>
+        <v>1.734</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.555</v>
+        <v>2.407</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>9.765000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.428</v>
+        <v>13.384</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>16.135</v>
+        <v>15.66</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -2389,22 +2389,22 @@
         <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>1.311</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>1.374</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>1.341</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.621</v>
       </c>
     </row>
     <row r="71">
@@ -2417,22 +2417,22 @@
         <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>1.311</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>1.374</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>1.341</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.621</v>
       </c>
     </row>
     <row r="72">
@@ -2529,19 +2529,19 @@
         <v>5.418</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.955</v>
+        <v>0.02</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2.558</v>
+        <v>1.184</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1.721</v>
+        <v>0.251</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>20.819</v>
+        <v>19.478</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>0</v>
@@ -2617,22 +2617,22 @@
         <v>0</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0</v>
+        <v>2.479</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0</v>
+        <v>1.692</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0</v>
+        <v>0.639</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0</v>
+        <v>1.939</v>
       </c>
     </row>
     <row r="79">
@@ -2645,22 +2645,22 @@
         <v>0</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>0</v>
+        <v>2.479</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>0</v>
+        <v>1.692</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0</v>
+        <v>0.639</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0</v>
+        <v>1.939</v>
       </c>
     </row>
     <row r="80">
@@ -2674,35 +2674,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C80" s="3" t="n">
+        <v>0.05346069527090511</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.02098543974488083</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.01595122027355354</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.04158041048086591</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.02588251588442029</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0.03455210484404313</v>
       </c>
     </row>
     <row r="81">
@@ -2827,19 +2815,19 @@
         <v>30.076</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>32.479</v>
+        <v>30</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>90.182</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>106.238</v>
+        <v>105.599</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>132.923</v>
+        <v>132.769</v>
       </c>
       <c r="H85" s="3" t="n">
         <v>0</v>
@@ -5136,7 +5124,11 @@
           <t>Lease obligations (Note 5)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -5281,7 +5273,11 @@
           <t>Lease obligations (Note 5)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -6294,7 +6290,11 @@
           <t>Lease obligations (Note 6)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -6488,7 +6488,11 @@
           <t>Lease obligations (Note 6)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -9978,7 +9982,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -12437,7 +12445,11 @@
           <t>Income tax (recovery) expense (Note 17)</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -14360,7 +14372,11 @@
           <t>Income tax (recovery) expense (Note 18)</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
